--- a/Trieur/verbe_rectifier_Franx.xlsx
+++ b/Trieur/verbe_rectifier_Franx.xlsx
@@ -455,7 +455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>matller</t>
+          <t>matllto</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>peto</t>
+          <t>pere</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>abetito</t>
+          <t>abetier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dañnnto</t>
+          <t>dañnnre</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aboolto</t>
+          <t>abooler</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>susivre</t>
+          <t>susivio</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>albccio</t>
+          <t>albccer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>refarer</t>
+          <t>refarre</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>revonto</t>
+          <t>revonre</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>alerire</t>
+          <t>aleriio</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>llerdto</t>
+          <t>llerder</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mueinre</t>
+          <t>mueinio</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aceerre</t>
+          <t>aceerer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>comntio</t>
+          <t>comntto</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>finnto</t>
+          <t>finnre</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>adhntio</t>
+          <t>adhntre</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>adontio</t>
+          <t>adonter</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DIRzzer</t>
+          <t>DIRzzto</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>aduerio</t>
+          <t>aduerto</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rebgger</t>
+          <t>rebggio</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>conrsto</t>
+          <t>conrsre</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Inesio</t>
+          <t>Inesto</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>acerdto</t>
+          <t>acerder</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>reciver</t>
+          <t>recivto</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>agaeder</t>
+          <t>agaedto</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>aguolio</t>
+          <t>aguoler</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>alarmre</t>
+          <t>alarmio</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Argrire</t>
+          <t>Argriio</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1667,7 +1667,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>todorio</t>
+          <t>todorto</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>volntio</t>
+          <t>volnter</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>arrosio</t>
+          <t>arrosto</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -1775,7 +1775,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>engalto</t>
+          <t>engalre</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -1787,7 +1787,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>peresio</t>
+          <t>pereser</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Párerto</t>
+          <t>Párerre</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ambosre</t>
+          <t>ambosio</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>paricer</t>
+          <t>paricto</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>amorsto</t>
+          <t>amorsre</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2063,7 +2063,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>prersto</t>
+          <t>prerser</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>anuller</t>
+          <t>anullre</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>apóofer</t>
+          <t>apóofio</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2267,7 +2267,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>apla er</t>
+          <t>apla to</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>argnter</t>
+          <t>argntre</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>patmto</t>
+          <t>patmer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>esfrsre</t>
+          <t>esfrser</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -2627,7 +2627,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>estoner</t>
+          <t>estonto</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>conurer</t>
+          <t>conurto</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>asticer</t>
+          <t>asticre</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>lusccre</t>
+          <t>lusccio</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -2891,7 +2891,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>aprurto</t>
+          <t>aprurre</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>tierrer</t>
+          <t>tierrto</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -2987,7 +2987,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>capeser</t>
+          <t>capesto</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>trainer</t>
+          <t>trainio</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>anterre</t>
+          <t>anterer</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3143,7 +3143,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>futurto</t>
+          <t>futurre</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3155,7 +3155,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>aveerto</t>
+          <t>aveerio</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3275,7 +3275,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>bacevio</t>
+          <t>bacevre</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -3287,7 +3287,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>cepolto</t>
+          <t>cepolio</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -3431,7 +3431,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>pénolio</t>
+          <t>pénolre</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>cabnnio</t>
+          <t>cabnnre</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -3491,7 +3491,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>panndio</t>
+          <t>pannder</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -3623,7 +3623,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>baratto</t>
+          <t>barater</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -3647,7 +3647,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>másilio</t>
+          <t>másilto</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>quiinto</t>
+          <t>quiinre</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -3671,7 +3671,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>batriio</t>
+          <t>batrire</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -3695,7 +3695,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Baundto</t>
+          <t>Baundio</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -3707,7 +3707,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>chaater</t>
+          <t>chaatio</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -3731,7 +3731,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>bazzaer</t>
+          <t>bazzaio</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -3791,7 +3791,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>cerrrio</t>
+          <t>cerrrre</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -3851,7 +3851,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>meire</t>
+          <t>meier</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -3911,7 +3911,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>manrrio</t>
+          <t>manrrre</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -3959,7 +3959,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>filchre</t>
+          <t>filcher</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -3971,7 +3971,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>en oger</t>
+          <t>en ogre</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>carilre</t>
+          <t>cariler</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4019,7 +4019,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>brorzto</t>
+          <t>brorzre</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4043,7 +4043,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>cullpio</t>
+          <t>cullpre</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4079,7 +4079,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>blemito</t>
+          <t>blemire</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>bluufto</t>
+          <t>bluufer</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -4175,7 +4175,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Bueerre</t>
+          <t>Bueerer</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>límitto</t>
+          <t>límiter</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -4199,7 +4199,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>traorer</t>
+          <t>traorio</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -4223,7 +4223,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>hebbiio</t>
+          <t>hebbier</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -4235,7 +4235,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>bliudre</t>
+          <t>bliuder</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -4247,7 +4247,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>borssre</t>
+          <t>borssio</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>amoonto</t>
+          <t>amoonio</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>movrsre</t>
+          <t>movrsio</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -4319,7 +4319,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>burllto</t>
+          <t>burllio</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -4379,7 +4379,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Becstto</t>
+          <t>Becster</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -4415,7 +4415,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>botlier</t>
+          <t>botliio</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -4487,7 +4487,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>hacrsto</t>
+          <t>hacrsre</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -4511,7 +4511,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>másosio</t>
+          <t>másosre</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>antalre</t>
+          <t>antalto</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -4607,7 +4607,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>herllio</t>
+          <t>herllre</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -4643,7 +4643,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>difurer</t>
+          <t>difurre</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>maronre</t>
+          <t>maronio</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -4727,7 +4727,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>apostto</t>
+          <t>apostre</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -4751,7 +4751,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>árbcato</t>
+          <t>árbcare</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -4763,7 +4763,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>árbcato</t>
+          <t>árbcaio</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -4787,7 +4787,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>selcer</t>
+          <t>selcre</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>cuainto</t>
+          <t>cuainre</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -4895,7 +4895,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>parllto</t>
+          <t>parller</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -4931,7 +4931,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>máslmio</t>
+          <t>máslmto</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -4943,7 +4943,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>calnito</t>
+          <t>calnier</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -4955,7 +4955,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>calicio</t>
+          <t>calicre</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>canenio</t>
+          <t>canenre</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -5039,7 +5039,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>cáncrer</t>
+          <t>cáncrto</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -5051,7 +5051,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>canolto</t>
+          <t>canolio</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -5111,7 +5111,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>carnter</t>
+          <t>carntto</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -5135,7 +5135,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>carzzio</t>
+          <t>carzzto</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -5147,7 +5147,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>carorto</t>
+          <t>carorio</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -5159,7 +5159,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>tellto</t>
+          <t>tellio</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -5219,7 +5219,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>cauuser</t>
+          <t>cauusio</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -5291,7 +5291,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>apaner</t>
+          <t>apanre</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -5303,7 +5303,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>cainto</t>
+          <t>cainio</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -5423,7 +5423,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>sildire</t>
+          <t>sildier</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -5435,7 +5435,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>desntio</t>
+          <t>desntto</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -5447,7 +5447,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>haberio</t>
+          <t>haberre</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>camutto</t>
+          <t>camutre</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>sitonre</t>
+          <t>sitoner</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>cazcier</t>
+          <t>cazcire</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -5627,7 +5627,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>cabttio</t>
+          <t>cabtter</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -5687,7 +5687,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>cmto</t>
+          <t>cmer</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>carrre</t>
+          <t>carrio</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -5807,7 +5807,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>tomicto</t>
+          <t>tomicre</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Pimpto</t>
+          <t>Pimper</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -5867,7 +5867,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>corer</t>
+          <t>corre</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -5891,7 +5891,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>agaedio</t>
+          <t>agaeder</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -5903,7 +5903,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>cuppre</t>
+          <t>cupper</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -5939,7 +5939,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>criorer</t>
+          <t>criorio</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -5975,7 +5975,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>cannio</t>
+          <t>cannto</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>limonto</t>
+          <t>limonio</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -6071,7 +6071,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>claarto</t>
+          <t>claarre</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -6095,7 +6095,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>chazzto</t>
+          <t>chazzio</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -6155,7 +6155,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>tecerre</t>
+          <t>tecerer</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -6179,7 +6179,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>desocio</t>
+          <t>desocre</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -6215,7 +6215,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>clatrto</t>
+          <t>clatrre</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -6239,7 +6239,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>claodre</t>
+          <t>claoder</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -6323,7 +6323,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>cointre</t>
+          <t>cointto</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>comntre</t>
+          <t>comntto</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -6563,7 +6563,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>halrsio</t>
+          <t>halrser</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -6647,7 +6647,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>oblivio</t>
+          <t>obliver</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -6683,7 +6683,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>cononre</t>
+          <t>cononer</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -6695,7 +6695,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>enfocre</t>
+          <t>enfocto</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>inqoner</t>
+          <t>inqonio</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>conntio</t>
+          <t>connter</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -6899,7 +6899,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>comorto</t>
+          <t>comorre</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -7019,7 +7019,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>connsio</t>
+          <t>connser</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>prervto</t>
+          <t>prerver</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -7043,7 +7043,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>cononre</t>
+          <t>cononer</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -7055,7 +7055,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>conllio</t>
+          <t>conllre</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -7091,7 +7091,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>aviisre</t>
+          <t>aviisio</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -7223,7 +7223,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>desider</t>
+          <t>desidre</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -7295,7 +7295,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>coneser</t>
+          <t>conesto</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -7343,7 +7343,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Conorto</t>
+          <t>Conorre</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -7355,7 +7355,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>conrsre</t>
+          <t>conrser</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>copicto</t>
+          <t>copicer</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -7511,7 +7511,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>coriver</t>
+          <t>corivio</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -7523,7 +7523,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>plaonre</t>
+          <t>plaonio</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -7583,7 +7583,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>desivio</t>
+          <t>desiver</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -7619,7 +7619,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>corinto</t>
+          <t>corinre</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -7631,7 +7631,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>dobrver</t>
+          <t>dobrvto</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -7655,7 +7655,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>corstre</t>
+          <t>corstto</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -7751,7 +7751,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>cubinio</t>
+          <t>cubiner</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -7811,7 +7811,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>griepto</t>
+          <t>grieper</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -7847,7 +7847,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>grieper</t>
+          <t>griepio</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -7859,7 +7859,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>atrosre</t>
+          <t>atrosio</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -7931,7 +7931,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>másnter</t>
+          <t>másntio</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -7967,7 +7967,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>crrsre</t>
+          <t>crrsto</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -8111,7 +8111,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>currto</t>
+          <t>currio</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -8123,7 +8123,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>digrsio</t>
+          <t>digrser</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -8159,7 +8159,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>pelolto</t>
+          <t>pelolio</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>fectio</t>
+          <t>fectto</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -8207,7 +8207,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>palerio</t>
+          <t>palerer</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>encntre</t>
+          <t>encntto</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -8327,7 +8327,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>debntio</t>
+          <t>debntto</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -8339,7 +8339,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>desinto</t>
+          <t>desinio</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -8387,7 +8387,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>desrsto</t>
+          <t>desrser</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -8399,7 +8399,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>afrnter</t>
+          <t>afrntre</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -8411,7 +8411,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>debntio</t>
+          <t>debntre</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -8579,7 +8579,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>debbber</t>
+          <t>debbbre</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -8603,7 +8603,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>decalto</t>
+          <t>decalio</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -8651,7 +8651,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>decntre</t>
+          <t>decnter</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -8687,7 +8687,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>decntio</t>
+          <t>decnter</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>desnter</t>
+          <t>desntre</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -8759,7 +8759,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>desntre</t>
+          <t>desntto</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -8915,7 +8915,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>adúerer</t>
+          <t>adúerre</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -8927,7 +8927,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>deslare</t>
+          <t>deslaio</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -8951,7 +8951,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Desntre</t>
+          <t>Desntio</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -8975,7 +8975,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>desodio</t>
+          <t>desoder</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -9059,7 +9059,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>deghire</t>
+          <t>deghier</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -9071,7 +9071,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>degerto</t>
+          <t>degerre</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -9083,7 +9083,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>gotccio</t>
+          <t>gotccto</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -9119,7 +9119,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>desouto</t>
+          <t>desoure</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -9203,7 +9203,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>comnzto</t>
+          <t>comnzio</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -9275,7 +9275,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>entgnio</t>
+          <t>entgnre</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>demonio</t>
+          <t>demonto</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -9395,7 +9395,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>resonre</t>
+          <t>resonio</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -9587,7 +9587,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>denerio</t>
+          <t>denerer</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -9599,7 +9599,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>frontto</t>
+          <t>fronter</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -9683,7 +9683,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>trantto</t>
+          <t>trantre</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -9731,7 +9731,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>repanto</t>
+          <t>repaner</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -9839,7 +9839,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>depssto</t>
+          <t>depssre</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -9875,7 +9875,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>ere</t>
+          <t>eto</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -9935,7 +9935,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>esaolio</t>
+          <t>esaolre</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -9971,7 +9971,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>últrser</t>
+          <t>últrsre</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -10043,7 +10043,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>desrsio</t>
+          <t>desrsto</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -10079,7 +10079,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>deszzio</t>
+          <t>deszzto</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -10103,7 +10103,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>desrgto</t>
+          <t>desrgio</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -10115,7 +10115,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>desoner</t>
+          <t>desonto</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -10127,7 +10127,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>desonio</t>
+          <t>desonre</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -10199,7 +10199,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>desssto</t>
+          <t>dessser</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -10223,7 +10223,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>desntre</t>
+          <t>desntio</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -10307,7 +10307,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>dibgnto</t>
+          <t>dibgnio</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -10343,7 +10343,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>desnaer</t>
+          <t>desnato</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -10391,7 +10391,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>detglto</t>
+          <t>detglre</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -10439,7 +10439,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>detntre</t>
+          <t>detntio</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -10451,7 +10451,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>disnter</t>
+          <t>disntre</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -10535,7 +10535,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>vamamre</t>
+          <t>vamamer</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -10547,7 +10547,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>devvare</t>
+          <t>devvaio</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -10655,7 +10655,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>derorre</t>
+          <t>derorto</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -10667,7 +10667,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>devtier</t>
+          <t>devtire</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -10799,7 +10799,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>diáogio</t>
+          <t>diáogre</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -10859,7 +10859,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>difrsio</t>
+          <t>difrsre</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -10931,7 +10931,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>cenio</t>
+          <t>cento</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -11219,7 +11219,7 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>estilre</t>
+          <t>estilto</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -11279,7 +11279,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>doroner</t>
+          <t>doronre</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -11327,7 +11327,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>dosser</t>
+          <t>dossre</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -11339,7 +11339,7 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>dosolre</t>
+          <t>dosolio</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -11363,7 +11363,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>ofialto</t>
+          <t>ofialio</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -11423,7 +11423,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>vesster</t>
+          <t>vesstto</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -11447,7 +11447,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>diersto</t>
+          <t>diersio</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -11495,7 +11495,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>durrsto</t>
+          <t>durrsio</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -11627,7 +11627,7 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>taberre</t>
+          <t>taberio</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>desocer</t>
+          <t>desocto</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -11771,7 +11771,7 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>esctcto</t>
+          <t>esctcer</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -11927,7 +11927,7 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>tocccio</t>
+          <t>tocccre</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
@@ -11963,7 +11963,7 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>hueaio</t>
+          <t>hueaer</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -12059,7 +12059,7 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>otogito</t>
+          <t>otogier</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -12071,7 +12071,7 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>estnter</t>
+          <t>estntto</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -12107,7 +12107,7 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>eloiger</t>
+          <t>eloigio</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -12131,7 +12131,7 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>eluivto</t>
+          <t>eluivio</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -12275,7 +12275,7 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>ofiicio</t>
+          <t>ofiicer</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -12311,7 +12311,7 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>premmto</t>
+          <t>premmre</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -12335,7 +12335,7 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>conusre</t>
+          <t>conuser</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
@@ -12359,7 +12359,7 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>prelito</t>
+          <t>prelier</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
@@ -12395,7 +12395,7 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>mudrsre</t>
+          <t>mudrsio</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -12443,7 +12443,7 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>movssio</t>
+          <t>movsser</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -12491,7 +12491,7 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>pilto</t>
+          <t>piler</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
@@ -12539,7 +12539,7 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>venener</t>
+          <t>venenre</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -12551,7 +12551,7 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>lleviio</t>
+          <t>llevito</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
@@ -12563,7 +12563,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>a lonio</t>
+          <t>a lonto</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -12647,7 +12647,7 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>Mieulto</t>
+          <t>Mieuler</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
@@ -12671,7 +12671,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>caunnto</t>
+          <t>caunnio</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
@@ -12719,7 +12719,7 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>eneio</t>
+          <t>eneto</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
@@ -13031,7 +13031,7 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>proelre</t>
+          <t>proelio</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
@@ -13187,7 +13187,7 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>amorsio</t>
+          <t>amorsre</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -13223,7 +13223,7 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>comerio</t>
+          <t>comerre</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
@@ -13343,7 +13343,7 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>visatre</t>
+          <t>visater</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
@@ -13403,7 +13403,7 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>envento</t>
+          <t>envener</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -13511,7 +13511,7 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>hallcre</t>
+          <t>hallcer</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
@@ -13535,7 +13535,7 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>épiicio</t>
+          <t>épiicre</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
@@ -13559,7 +13559,7 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>epilere</t>
+          <t>epileto</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
@@ -13631,7 +13631,7 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>prusto</t>
+          <t>prusre</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
@@ -13643,7 +13643,7 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>escicto</t>
+          <t>escicio</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -13715,7 +13715,7 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>hominre</t>
+          <t>hominer</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
@@ -13763,7 +13763,7 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>eroodio</t>
+          <t>erooder</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
@@ -13787,7 +13787,7 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>treatio</t>
+          <t>treatre</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
@@ -13799,7 +13799,7 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>escalio</t>
+          <t>escalto</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
@@ -13859,7 +13859,7 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>espnzre</t>
+          <t>espnzer</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
@@ -13883,7 +13883,7 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>espnzto</t>
+          <t>espnzre</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
@@ -13895,7 +13895,7 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>boszzio</t>
+          <t>boszzre</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
@@ -13955,7 +13955,7 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>esterio</t>
+          <t>esterto</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
@@ -13979,7 +13979,7 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>estpire</t>
+          <t>estpier</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
@@ -14003,7 +14003,7 @@
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>extonio</t>
+          <t>extonto</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
@@ -14015,7 +14015,7 @@
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>etáerio</t>
+          <t>etáerre</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
@@ -14027,7 +14027,7 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>selcto</t>
+          <t>selcre</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
@@ -14075,7 +14075,7 @@
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>estatre</t>
+          <t>estatto</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
@@ -14087,7 +14087,7 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>soresto</t>
+          <t>soresre</t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
@@ -14135,7 +14135,7 @@
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>calbrio</t>
+          <t>calbrer</t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
@@ -14219,7 +14219,7 @@
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>hunllre</t>
+          <t>hunllto</t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
@@ -14375,7 +14375,7 @@
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>disusio</t>
+          <t>disuser</t>
         </is>
       </c>
       <c r="B1164" t="inlineStr">
@@ -14531,7 +14531,7 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>expnter</t>
+          <t>expntre</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
@@ -14543,7 +14543,7 @@
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>exponer</t>
+          <t>exponto</t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
@@ -14615,7 +14615,7 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>expeser</t>
+          <t>expesio</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
@@ -14759,7 +14759,7 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>alenzer</t>
+          <t>alenzto</t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
@@ -14783,7 +14783,7 @@
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>asitter</t>
+          <t>asittio</t>
         </is>
       </c>
       <c r="B1198" t="inlineStr">
@@ -14807,7 +14807,7 @@
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>forrmto</t>
+          <t>forrmer</t>
         </is>
       </c>
       <c r="B1200" t="inlineStr">
@@ -14879,7 +14879,7 @@
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>famlire</t>
+          <t>famlito</t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
@@ -14891,7 +14891,7 @@
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>banerre</t>
+          <t>banerto</t>
         </is>
       </c>
       <c r="B1207" t="inlineStr">
@@ -14903,7 +14903,7 @@
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>prersio</t>
+          <t>prerser</t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
@@ -14927,7 +14927,7 @@
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>másanto</t>
+          <t>másanre</t>
         </is>
       </c>
       <c r="B1210" t="inlineStr">
@@ -14951,7 +14951,7 @@
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>canncto</t>
+          <t>canncre</t>
         </is>
       </c>
       <c r="B1212" t="inlineStr">
@@ -15047,7 +15047,7 @@
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>errorer</t>
+          <t>errorto</t>
         </is>
       </c>
       <c r="B1220" t="inlineStr">
@@ -15059,7 +15059,7 @@
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>exissio</t>
+          <t>exisser</t>
         </is>
       </c>
       <c r="B1221" t="inlineStr">
@@ -15083,7 +15083,7 @@
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>Fer</t>
+          <t>Fre</t>
         </is>
       </c>
       <c r="B1223" t="inlineStr">
@@ -15119,7 +15119,7 @@
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>agriner</t>
+          <t>agrinio</t>
         </is>
       </c>
       <c r="B1226" t="inlineStr">
@@ -15143,7 +15143,7 @@
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>ferntto</t>
+          <t>ferntre</t>
         </is>
       </c>
       <c r="B1228" t="inlineStr">
@@ -15167,7 +15167,7 @@
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>banstre</t>
+          <t>banster</t>
         </is>
       </c>
       <c r="B1230" t="inlineStr">
@@ -15215,7 +15215,7 @@
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>comrser</t>
+          <t>comrsto</t>
         </is>
       </c>
       <c r="B1234" t="inlineStr">
@@ -15251,7 +15251,7 @@
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>fidelto</t>
+          <t>fideler</t>
         </is>
       </c>
       <c r="B1237" t="inlineStr">
@@ -15263,7 +15263,7 @@
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>hierrio</t>
+          <t>hierrto</t>
         </is>
       </c>
       <c r="B1238" t="inlineStr">
@@ -15275,7 +15275,7 @@
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>árbchre</t>
+          <t>árbchto</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
@@ -15335,7 +15335,7 @@
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>filtrer</t>
+          <t>filtrto</t>
         </is>
       </c>
       <c r="B1244" t="inlineStr">
@@ -15371,7 +15371,7 @@
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>ternto</t>
+          <t>ternre</t>
         </is>
       </c>
       <c r="B1247" t="inlineStr">
@@ -15407,7 +15407,7 @@
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>griepto</t>
+          <t>grieper</t>
         </is>
       </c>
       <c r="B1250" t="inlineStr">
@@ -15443,7 +15443,7 @@
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>astrnto</t>
+          <t>astrnre</t>
         </is>
       </c>
       <c r="B1253" t="inlineStr">
@@ -15479,7 +15479,7 @@
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>resater</t>
+          <t>resatto</t>
         </is>
       </c>
       <c r="B1256" t="inlineStr">
@@ -15491,7 +15491,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>flantre</t>
+          <t>flantio</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -15515,7 +15515,7 @@
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>flancio</t>
+          <t>flancre</t>
         </is>
       </c>
       <c r="B1259" t="inlineStr">
@@ -15599,7 +15599,7 @@
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>flonter</t>
+          <t>flontto</t>
         </is>
       </c>
       <c r="B1266" t="inlineStr">
@@ -15659,7 +15659,7 @@
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>tierrto</t>
+          <t>tierrer</t>
         </is>
       </c>
       <c r="B1271" t="inlineStr">
@@ -15671,7 +15671,7 @@
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>funonto</t>
+          <t>funonre</t>
         </is>
       </c>
       <c r="B1272" t="inlineStr">
@@ -15683,7 +15683,7 @@
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>carosio</t>
+          <t>carosre</t>
         </is>
       </c>
       <c r="B1273" t="inlineStr">
@@ -15695,7 +15695,7 @@
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>forrzre</t>
+          <t>forrzer</t>
         </is>
       </c>
       <c r="B1274" t="inlineStr">
@@ -15707,7 +15707,7 @@
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>forrzre</t>
+          <t>forrzio</t>
         </is>
       </c>
       <c r="B1275" t="inlineStr">
@@ -15719,7 +15719,7 @@
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>priimre</t>
+          <t>priimio</t>
         </is>
       </c>
       <c r="B1276" t="inlineStr">
@@ -15731,7 +15731,7 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>SILURio</t>
+          <t>SILURto</t>
         </is>
       </c>
       <c r="B1277" t="inlineStr">
@@ -15791,7 +15791,7 @@
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>fosrsto</t>
+          <t>fosrsre</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
@@ -15803,7 +15803,7 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>látstio</t>
+          <t>látstre</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
@@ -15839,7 +15839,7 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>cuatrre</t>
+          <t>cuatrer</t>
         </is>
       </c>
       <c r="B1286" t="inlineStr">
@@ -15911,7 +15911,7 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>costo</t>
+          <t>coser</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
@@ -15923,7 +15923,7 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>ofitrio</t>
+          <t>ofitrre</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
@@ -15935,7 +15935,7 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>desinre</t>
+          <t>desinio</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
@@ -15971,7 +15971,7 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>fraurio</t>
+          <t>fraurer</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
@@ -15983,7 +15983,7 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>molinre</t>
+          <t>molinto</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
@@ -15995,7 +15995,7 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>arbonto</t>
+          <t>arbonio</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
@@ -16019,7 +16019,7 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>gollpto</t>
+          <t>gollper</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
@@ -16043,7 +16043,7 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>freenio</t>
+          <t>freenre</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
@@ -16103,7 +16103,7 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>frierre</t>
+          <t>frierer</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
@@ -16151,7 +16151,7 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>arrnzio</t>
+          <t>arrnzer</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
@@ -16235,7 +16235,7 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>estamre</t>
+          <t>estamio</t>
         </is>
       </c>
       <c r="B1319" t="inlineStr">
@@ -16307,7 +16307,7 @@
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>ganriio</t>
+          <t>ganrito</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
@@ -16355,7 +16355,7 @@
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>Desnsio</t>
+          <t>Desnsto</t>
         </is>
       </c>
       <c r="B1329" t="inlineStr">
@@ -16403,7 +16403,7 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>guarnto</t>
+          <t>guarnio</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
@@ -16427,7 +16427,7 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>caladto</t>
+          <t>caladre</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
@@ -16463,7 +16463,7 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>regalre</t>
+          <t>regaler</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
@@ -16475,7 +16475,7 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>venrrre</t>
+          <t>venrrer</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
@@ -16487,7 +16487,7 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>Gemllio</t>
+          <t>Gemllto</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
@@ -16535,7 +16535,7 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>Ginvrio</t>
+          <t>Ginvrto</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
@@ -16595,7 +16595,7 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>gessiio</t>
+          <t>gessito</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
@@ -16619,7 +16619,7 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>jueinre</t>
+          <t>jueiner</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
@@ -16631,7 +16631,7 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>bofffto</t>
+          <t>bofffer</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
@@ -16643,7 +16643,7 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>agirser</t>
+          <t>agirsio</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
@@ -16691,7 +16691,7 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>glaesre</t>
+          <t>glaesio</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
@@ -16703,7 +16703,7 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>glapiio</t>
+          <t>glapito</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
@@ -16751,7 +16751,7 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>gobrnto</t>
+          <t>gobrnio</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
@@ -16787,7 +16787,7 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>garlto</t>
+          <t>garlre</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
@@ -16811,7 +16811,7 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>alqamer</t>
+          <t>alqamio</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
@@ -16823,7 +16823,7 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>prorsre</t>
+          <t>prorsto</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
@@ -16835,7 +16835,7 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>gotter</t>
+          <t>gottio</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
@@ -16859,7 +16859,7 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>indusio</t>
+          <t>industo</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
@@ -16871,7 +16871,7 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>grasser</t>
+          <t>grassio</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
@@ -16907,7 +16907,7 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>rasrtto</t>
+          <t>rasrter</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
@@ -16931,7 +16931,7 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>graaver</t>
+          <t>graavto</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
@@ -16943,7 +16943,7 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>graaiio</t>
+          <t>graaier</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
@@ -16967,7 +16967,7 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>injonto</t>
+          <t>injoner</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
@@ -16979,7 +16979,7 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>temidio</t>
+          <t>temidre</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
@@ -16991,7 +16991,7 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>grentto</t>
+          <t>grentio</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
@@ -17015,7 +17015,7 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>grionto</t>
+          <t>grionre</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
@@ -17027,7 +17027,7 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>Parlito</t>
+          <t>Parliio</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
@@ -17039,7 +17039,7 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>másupre</t>
+          <t>másupto</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
@@ -17063,7 +17063,7 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>chiocto</t>
+          <t>chiocio</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
@@ -17075,7 +17075,7 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>ceralto</t>
+          <t>ceralre</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
@@ -17123,7 +17123,7 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>groanio</t>
+          <t>groaner</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
@@ -17147,7 +17147,7 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>crender</t>
+          <t>crendre</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
@@ -17171,7 +17171,7 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>agrnier</t>
+          <t>agrnire</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
@@ -17195,7 +17195,7 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>gueerre</t>
+          <t>gueerio</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
@@ -17207,7 +17207,7 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>a lrrre</t>
+          <t>a lrrto</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
@@ -17303,7 +17303,7 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>crder</t>
+          <t>crdre</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
@@ -17315,7 +17315,7 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>sitonto</t>
+          <t>sitonio</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
@@ -17327,7 +17327,7 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>aluonre</t>
+          <t>aluoner</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
@@ -17339,7 +17339,7 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>agaeder</t>
+          <t>agaedto</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
@@ -17411,7 +17411,7 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>anfitto</t>
+          <t>anfitio</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
@@ -17459,7 +17459,7 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>heredre</t>
+          <t>hereder</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
@@ -17507,7 +17507,7 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>aqer</t>
+          <t>aqre</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
@@ -17543,7 +17543,7 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>invrner</t>
+          <t>invrnio</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
@@ -17555,7 +17555,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>asennto</t>
+          <t>asennre</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -17567,7 +17567,7 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>Honicto</t>
+          <t>Honicio</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
@@ -17579,7 +17579,7 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>es ento</t>
+          <t>es enio</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
@@ -17603,7 +17603,7 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>hizzer</t>
+          <t>hizzre</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
@@ -17627,7 +17627,7 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>hosalre</t>
+          <t>hosalio</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
@@ -17783,7 +17783,7 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>idótrer</t>
+          <t>idótrio</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
@@ -17951,7 +17951,7 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>impicto</t>
+          <t>impicer</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
@@ -18155,7 +18155,7 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>caricio</t>
+          <t>caricer</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
@@ -18167,7 +18167,7 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>currvio</t>
+          <t>currvre</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
@@ -18239,7 +18239,7 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>infhiio</t>
+          <t>infhito</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
@@ -18371,7 +18371,7 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>difonio</t>
+          <t>difonre</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
@@ -18395,7 +18395,7 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>inuonto</t>
+          <t>inuonre</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
@@ -18407,7 +18407,7 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>preonre</t>
+          <t>preonio</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
@@ -18587,7 +18587,7 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>intrner</t>
+          <t>intrnio</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
@@ -18611,7 +18611,7 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>intetto</t>
+          <t>intetio</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
@@ -18623,7 +18623,7 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>prender</t>
+          <t>prendre</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
@@ -18671,7 +18671,7 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>intigre</t>
+          <t>intigio</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
@@ -18839,7 +18839,7 @@
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>celosto</t>
+          <t>celosre</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
@@ -18887,7 +18887,7 @@
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>chaatto</t>
+          <t>chaatre</t>
         </is>
       </c>
       <c r="B1540" t="inlineStr">
@@ -18899,7 +18899,7 @@
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>indurto</t>
+          <t>indurer</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
@@ -18911,7 +18911,7 @@
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>amallto</t>
+          <t>amallre</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
@@ -18983,7 +18983,7 @@
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>a danre</t>
+          <t>a danio</t>
         </is>
       </c>
       <c r="B1548" t="inlineStr">
@@ -19007,7 +19007,7 @@
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>juicio</t>
+          <t>juicer</t>
         </is>
       </c>
       <c r="B1550" t="inlineStr">
@@ -19019,7 +19019,7 @@
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>Júpovre</t>
+          <t>Júpovto</t>
         </is>
       </c>
       <c r="B1551" t="inlineStr">
@@ -19043,7 +19043,7 @@
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>vignter</t>
+          <t>vigntre</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
@@ -19259,7 +19259,7 @@
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>barccer</t>
+          <t>barccio</t>
         </is>
       </c>
       <c r="B1571" t="inlineStr">
@@ -19295,7 +19295,7 @@
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>neuicto</t>
+          <t>neuicer</t>
         </is>
       </c>
       <c r="B1574" t="inlineStr">
@@ -19307,7 +19307,7 @@
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>lavncio</t>
+          <t>lavncre</t>
         </is>
       </c>
       <c r="B1575" t="inlineStr">
@@ -19319,7 +19319,7 @@
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>lídper</t>
+          <t>lídpio</t>
         </is>
       </c>
       <c r="B1576" t="inlineStr">
@@ -19331,7 +19331,7 @@
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>lamater</t>
+          <t>lamatre</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
@@ -19367,7 +19367,7 @@
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>másimre</t>
+          <t>másimer</t>
         </is>
       </c>
       <c r="B1580" t="inlineStr">
@@ -19391,7 +19391,7 @@
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>Negrer</t>
+          <t>Negrto</t>
         </is>
       </c>
       <c r="B1582" t="inlineStr">
@@ -19439,7 +19439,7 @@
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>lggto</t>
+          <t>lggio</t>
         </is>
       </c>
       <c r="B1586" t="inlineStr">
@@ -19463,7 +19463,7 @@
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>palver</t>
+          <t>palvre</t>
         </is>
       </c>
       <c r="B1588" t="inlineStr">
@@ -19559,7 +19559,7 @@
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>adhivto</t>
+          <t>adhivre</t>
         </is>
       </c>
       <c r="B1596" t="inlineStr">
@@ -19643,7 +19643,7 @@
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>casio</t>
+          <t>casto</t>
         </is>
       </c>
       <c r="B1603" t="inlineStr">
@@ -19655,7 +19655,7 @@
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>lirirre</t>
+          <t>liririo</t>
         </is>
       </c>
       <c r="B1604" t="inlineStr">
@@ -19667,7 +19667,7 @@
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>ocerer</t>
+          <t>ocerre</t>
         </is>
       </c>
       <c r="B1605" t="inlineStr">
@@ -19703,7 +19703,7 @@
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>viratio</t>
+          <t>virater</t>
         </is>
       </c>
       <c r="B1608" t="inlineStr">
@@ -19763,7 +19763,7 @@
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>masosio</t>
+          <t>masosre</t>
         </is>
       </c>
       <c r="B1613" t="inlineStr">
@@ -19811,7 +19811,7 @@
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>tabolio</t>
+          <t>tabolto</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
@@ -19823,7 +19823,7 @@
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>peresto</t>
+          <t>pereser</t>
         </is>
       </c>
       <c r="B1618" t="inlineStr">
@@ -19931,7 +19931,7 @@
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>pesoiio</t>
+          <t>pesoire</t>
         </is>
       </c>
       <c r="B1627" t="inlineStr">
@@ -19943,7 +19943,7 @@
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>fordto</t>
+          <t>fordre</t>
         </is>
       </c>
       <c r="B1628" t="inlineStr">
@@ -20003,7 +20003,7 @@
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>conccio</t>
+          <t>conccre</t>
         </is>
       </c>
       <c r="B1633" t="inlineStr">
@@ -20063,7 +20063,7 @@
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>marder</t>
+          <t>mardre</t>
         </is>
       </c>
       <c r="B1638" t="inlineStr">
@@ -20099,7 +20099,7 @@
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>Arbgnio</t>
+          <t>Arbgnto</t>
         </is>
       </c>
       <c r="B1641" t="inlineStr">
@@ -20147,7 +20147,7 @@
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>mascrer</t>
+          <t>mascrto</t>
         </is>
       </c>
       <c r="B1645" t="inlineStr">
@@ -20183,7 +20183,7 @@
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>medlito</t>
+          <t>medliio</t>
         </is>
       </c>
       <c r="B1648" t="inlineStr">
@@ -20195,7 +20195,7 @@
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>en zzer</t>
+          <t>en zzre</t>
         </is>
       </c>
       <c r="B1649" t="inlineStr">
@@ -20207,7 +20207,7 @@
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>señorer</t>
+          <t>señorio</t>
         </is>
       </c>
       <c r="B1650" t="inlineStr">
@@ -20231,7 +20231,7 @@
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>melngto</t>
+          <t>melnger</t>
         </is>
       </c>
       <c r="B1652" t="inlineStr">
@@ -20243,7 +20243,7 @@
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>balio</t>
+          <t>balre</t>
         </is>
       </c>
       <c r="B1653" t="inlineStr">
@@ -20279,7 +20279,7 @@
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>amangto</t>
+          <t>amangio</t>
         </is>
       </c>
       <c r="B1656" t="inlineStr">
@@ -20351,7 +20351,7 @@
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>caramto</t>
+          <t>caramio</t>
         </is>
       </c>
       <c r="B1662" t="inlineStr">
@@ -20375,7 +20375,7 @@
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>mio</t>
+          <t>mre</t>
         </is>
       </c>
       <c r="B1664" t="inlineStr">
@@ -20387,7 +20387,7 @@
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>méritto</t>
+          <t>méritre</t>
         </is>
       </c>
       <c r="B1665" t="inlineStr">
@@ -20399,7 +20399,7 @@
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>horiler</t>
+          <t>horilre</t>
         </is>
       </c>
       <c r="B1666" t="inlineStr">
@@ -20447,7 +20447,7 @@
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>emparer</t>
+          <t>emparre</t>
         </is>
       </c>
       <c r="B1670" t="inlineStr">
@@ -20483,7 +20483,7 @@
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>mettrto</t>
+          <t>mettrer</t>
         </is>
       </c>
       <c r="B1673" t="inlineStr">
@@ -20519,7 +20519,7 @@
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>aseinre</t>
+          <t>aseiner</t>
         </is>
       </c>
       <c r="B1676" t="inlineStr">
@@ -20579,7 +20579,7 @@
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>mllto</t>
+          <t>mllre</t>
         </is>
       </c>
       <c r="B1681" t="inlineStr">
@@ -20603,7 +20603,7 @@
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>minonre</t>
+          <t>minonto</t>
         </is>
       </c>
       <c r="B1683" t="inlineStr">
@@ -20639,7 +20639,7 @@
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>mirio</t>
+          <t>mirto</t>
         </is>
       </c>
       <c r="B1686" t="inlineStr">
@@ -20663,7 +20663,7 @@
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>avaario</t>
+          <t>avaarre</t>
         </is>
       </c>
       <c r="B1688" t="inlineStr">
@@ -20675,7 +20675,7 @@
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>muelito</t>
+          <t>muelier</t>
         </is>
       </c>
       <c r="B1689" t="inlineStr">
@@ -20711,7 +20711,7 @@
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>maddrto</t>
+          <t>maddrre</t>
         </is>
       </c>
       <c r="B1692" t="inlineStr">
@@ -20843,7 +20843,7 @@
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>motivto</t>
+          <t>motivio</t>
         </is>
       </c>
       <c r="B1703" t="inlineStr">
@@ -20891,7 +20891,7 @@
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>moffre</t>
+          <t>moffer</t>
         </is>
       </c>
       <c r="B1707" t="inlineStr">
@@ -20915,7 +20915,7 @@
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>movsser</t>
+          <t>movssre</t>
         </is>
       </c>
       <c r="B1709" t="inlineStr">
@@ -20951,7 +20951,7 @@
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>munnier</t>
+          <t>munnito</t>
         </is>
       </c>
       <c r="B1712" t="inlineStr">
@@ -20963,7 +20963,7 @@
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>madurto</t>
+          <t>madurio</t>
         </is>
       </c>
       <c r="B1713" t="inlineStr">
@@ -20975,7 +20975,7 @@
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>susrrto</t>
+          <t>susrrre</t>
         </is>
       </c>
       <c r="B1714" t="inlineStr">
@@ -21035,7 +21035,7 @@
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>tonchio</t>
+          <t>tonchre</t>
         </is>
       </c>
       <c r="B1719" t="inlineStr">
@@ -21095,7 +21095,7 @@
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>desurer</t>
+          <t>desurto</t>
         </is>
       </c>
       <c r="B1724" t="inlineStr">
@@ -21191,7 +21191,7 @@
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>chinzer</t>
+          <t>chinzto</t>
         </is>
       </c>
       <c r="B1732" t="inlineStr">
@@ -21215,7 +21215,7 @@
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>nivllio</t>
+          <t>nivllto</t>
         </is>
       </c>
       <c r="B1734" t="inlineStr">
@@ -21239,7 +21239,7 @@
     <row r="1736">
       <c r="A1736" t="inlineStr">
         <is>
-          <t>cololer</t>
+          <t>cololre</t>
         </is>
       </c>
       <c r="B1736" t="inlineStr">
@@ -21275,7 +21275,7 @@
     <row r="1739">
       <c r="A1739" t="inlineStr">
         <is>
-          <t>attter</t>
+          <t>atttio</t>
         </is>
       </c>
       <c r="B1739" t="inlineStr">
@@ -21359,7 +21359,7 @@
     <row r="1746">
       <c r="A1746" t="inlineStr">
         <is>
-          <t>borllio</t>
+          <t>borller</t>
         </is>
       </c>
       <c r="B1746" t="inlineStr">
@@ -21371,7 +21371,7 @@
     <row r="1747">
       <c r="A1747" t="inlineStr">
         <is>
-          <t>oscurer</t>
+          <t>oscurio</t>
         </is>
       </c>
       <c r="B1747" t="inlineStr">
@@ -21383,7 +21383,7 @@
     <row r="1748">
       <c r="A1748" t="inlineStr">
         <is>
-          <t>obsivio</t>
+          <t>obsiver</t>
         </is>
       </c>
       <c r="B1748" t="inlineStr">
@@ -21431,7 +21431,7 @@
     <row r="1752">
       <c r="A1752" t="inlineStr">
         <is>
-          <t>cauuser</t>
+          <t>cauusio</t>
         </is>
       </c>
       <c r="B1752" t="inlineStr">
@@ -21467,7 +21467,7 @@
     <row r="1755">
       <c r="A1755" t="inlineStr">
         <is>
-          <t>traorre</t>
+          <t>traorto</t>
         </is>
       </c>
       <c r="B1755" t="inlineStr">
@@ -21491,7 +21491,7 @@
     <row r="1757">
       <c r="A1757" t="inlineStr">
         <is>
-          <t>ofialer</t>
+          <t>ofialio</t>
         </is>
       </c>
       <c r="B1757" t="inlineStr">
@@ -21563,7 +21563,7 @@
     <row r="1763">
       <c r="A1763" t="inlineStr">
         <is>
-          <t>oporsto</t>
+          <t>oporser</t>
         </is>
       </c>
       <c r="B1763" t="inlineStr">
@@ -21599,7 +21599,7 @@
     <row r="1766">
       <c r="A1766" t="inlineStr">
         <is>
-          <t>Narncto</t>
+          <t>Narncre</t>
         </is>
       </c>
       <c r="B1766" t="inlineStr">
@@ -21623,7 +21623,7 @@
     <row r="1768">
       <c r="A1768" t="inlineStr">
         <is>
-          <t>alminio</t>
+          <t>alminre</t>
         </is>
       </c>
       <c r="B1768" t="inlineStr">
@@ -21707,7 +21707,7 @@
     <row r="1775">
       <c r="A1775" t="inlineStr">
         <is>
-          <t>Nuttrer</t>
+          <t>Nuttrre</t>
         </is>
       </c>
       <c r="B1775" t="inlineStr">
@@ -21731,7 +21731,7 @@
     <row r="1777">
       <c r="A1777" t="inlineStr">
         <is>
-          <t>nuetrer</t>
+          <t>nuetrio</t>
         </is>
       </c>
       <c r="B1777" t="inlineStr">
@@ -21743,7 +21743,7 @@
     <row r="1778">
       <c r="A1778" t="inlineStr">
         <is>
-          <t>nuediio</t>
+          <t>nuedire</t>
         </is>
       </c>
       <c r="B1778" t="inlineStr">
@@ -21755,7 +21755,7 @@
     <row r="1779">
       <c r="A1779" t="inlineStr">
         <is>
-          <t>indosre</t>
+          <t>indoser</t>
         </is>
       </c>
       <c r="B1779" t="inlineStr">
@@ -21779,7 +21779,7 @@
     <row r="1781">
       <c r="A1781" t="inlineStr">
         <is>
-          <t>foremer</t>
+          <t>foremto</t>
         </is>
       </c>
       <c r="B1781" t="inlineStr">
@@ -21815,7 +21815,7 @@
     <row r="1784">
       <c r="A1784" t="inlineStr">
         <is>
-          <t>ovastio</t>
+          <t>ovastre</t>
         </is>
       </c>
       <c r="B1784" t="inlineStr">
@@ -21875,7 +21875,7 @@
     <row r="1789">
       <c r="A1789" t="inlineStr">
         <is>
-          <t>ateodto</t>
+          <t>ateoder</t>
         </is>
       </c>
       <c r="B1789" t="inlineStr">
@@ -21887,7 +21887,7 @@
     <row r="1790">
       <c r="A1790" t="inlineStr">
         <is>
-          <t>ler</t>
+          <t>lto</t>
         </is>
       </c>
       <c r="B1790" t="inlineStr">
@@ -21911,7 +21911,7 @@
     <row r="1792">
       <c r="A1792" t="inlineStr">
         <is>
-          <t>pallmto</t>
+          <t>pallmio</t>
         </is>
       </c>
       <c r="B1792" t="inlineStr">
@@ -22019,7 +22019,7 @@
     <row r="1801">
       <c r="A1801" t="inlineStr">
         <is>
-          <t>papstio</t>
+          <t>papstto</t>
         </is>
       </c>
       <c r="B1801" t="inlineStr">
@@ -22031,7 +22031,7 @@
     <row r="1802">
       <c r="A1802" t="inlineStr">
         <is>
-          <t>chaatio</t>
+          <t>chaatre</t>
         </is>
       </c>
       <c r="B1802" t="inlineStr">
@@ -22175,7 +22175,7 @@
     <row r="1814">
       <c r="A1814" t="inlineStr">
         <is>
-          <t>pardiio</t>
+          <t>pardier</t>
         </is>
       </c>
       <c r="B1814" t="inlineStr">
@@ -22259,7 +22259,7 @@
     <row r="1821">
       <c r="A1821" t="inlineStr">
         <is>
-          <t>pasntio</t>
+          <t>pasntre</t>
         </is>
       </c>
       <c r="B1821" t="inlineStr">
@@ -22355,7 +22355,7 @@
     <row r="1829">
       <c r="A1829" t="inlineStr">
         <is>
-          <t>Pauerre</t>
+          <t>Pauerio</t>
         </is>
       </c>
       <c r="B1829" t="inlineStr">
@@ -22643,7 +22643,7 @@
     <row r="1853">
       <c r="A1853" t="inlineStr">
         <is>
-          <t>pertuto</t>
+          <t>perture</t>
         </is>
       </c>
       <c r="B1853" t="inlineStr">
@@ -22691,7 +22691,7 @@
     <row r="1857">
       <c r="A1857" t="inlineStr">
         <is>
-          <t>perntre</t>
+          <t>pernter</t>
         </is>
       </c>
       <c r="B1857" t="inlineStr">
@@ -22811,7 +22811,7 @@
     <row r="1867">
       <c r="A1867" t="inlineStr">
         <is>
-          <t>pettrre</t>
+          <t>pettrer</t>
         </is>
       </c>
       <c r="B1867" t="inlineStr">
@@ -22823,7 +22823,7 @@
     <row r="1868">
       <c r="A1868" t="inlineStr">
         <is>
-          <t>petrnio</t>
+          <t>petrnto</t>
         </is>
       </c>
       <c r="B1868" t="inlineStr">
@@ -22859,7 +22859,7 @@
     <row r="1871">
       <c r="A1871" t="inlineStr">
         <is>
-          <t>fotfire</t>
+          <t>fotfiio</t>
         </is>
       </c>
       <c r="B1871" t="inlineStr">
@@ -22931,7 +22931,7 @@
     <row r="1877">
       <c r="A1877" t="inlineStr">
         <is>
-          <t>paloner</t>
+          <t>palonto</t>
         </is>
       </c>
       <c r="B1877" t="inlineStr">
@@ -22943,7 +22943,7 @@
     <row r="1878">
       <c r="A1878" t="inlineStr">
         <is>
-          <t>chizzto</t>
+          <t>chizzio</t>
         </is>
       </c>
       <c r="B1878" t="inlineStr">
@@ -22955,7 +22955,7 @@
     <row r="1879">
       <c r="A1879" t="inlineStr">
         <is>
-          <t>piltrre</t>
+          <t>piltrio</t>
         </is>
       </c>
       <c r="B1879" t="inlineStr">
@@ -22979,7 +22979,7 @@
     <row r="1881">
       <c r="A1881" t="inlineStr">
         <is>
-          <t>pilotio</t>
+          <t>pilotto</t>
         </is>
       </c>
       <c r="B1881" t="inlineStr">
@@ -23003,7 +23003,7 @@
     <row r="1883">
       <c r="A1883" t="inlineStr">
         <is>
-          <t>pinlire</t>
+          <t>pinliio</t>
         </is>
       </c>
       <c r="B1883" t="inlineStr">
@@ -23015,7 +23015,7 @@
     <row r="1884">
       <c r="A1884" t="inlineStr">
         <is>
-          <t>dibgner</t>
+          <t>dibgnio</t>
         </is>
       </c>
       <c r="B1884" t="inlineStr">
@@ -23039,7 +23039,7 @@
     <row r="1886">
       <c r="A1886" t="inlineStr">
         <is>
-          <t>picurer</t>
+          <t>picurto</t>
         </is>
       </c>
       <c r="B1886" t="inlineStr">
@@ -23075,7 +23075,7 @@
     <row r="1889">
       <c r="A1889" t="inlineStr">
         <is>
-          <t>lámerre</t>
+          <t>lámerer</t>
         </is>
       </c>
       <c r="B1889" t="inlineStr">
@@ -23123,7 +23123,7 @@
     <row r="1893">
       <c r="A1893" t="inlineStr">
         <is>
-          <t>broirre</t>
+          <t>broirto</t>
         </is>
       </c>
       <c r="B1893" t="inlineStr">
@@ -23183,7 +23183,7 @@
     <row r="1898">
       <c r="A1898" t="inlineStr">
         <is>
-          <t>plaerio</t>
+          <t>plaerto</t>
         </is>
       </c>
       <c r="B1898" t="inlineStr">
@@ -23195,7 +23195,7 @@
     <row r="1899">
       <c r="A1899" t="inlineStr">
         <is>
-          <t>yeltto</t>
+          <t>yeltio</t>
         </is>
       </c>
       <c r="B1899" t="inlineStr">
@@ -23231,7 +23231,7 @@
     <row r="1902">
       <c r="A1902" t="inlineStr">
         <is>
-          <t>dobrvto</t>
+          <t>dobrver</t>
         </is>
       </c>
       <c r="B1902" t="inlineStr">
@@ -23255,7 +23255,7 @@
     <row r="1904">
       <c r="A1904" t="inlineStr">
         <is>
-          <t>ploicer</t>
+          <t>ploicre</t>
         </is>
       </c>
       <c r="B1904" t="inlineStr">
@@ -23279,7 +23279,7 @@
     <row r="1906">
       <c r="A1906" t="inlineStr">
         <is>
-          <t>dobrvre</t>
+          <t>dobrver</t>
         </is>
       </c>
       <c r="B1906" t="inlineStr">
@@ -23303,7 +23303,7 @@
     <row r="1908">
       <c r="A1908" t="inlineStr">
         <is>
-          <t>plainio</t>
+          <t>plainer</t>
         </is>
       </c>
       <c r="B1908" t="inlineStr">
@@ -23363,7 +23363,7 @@
     <row r="1913">
       <c r="A1913" t="inlineStr">
         <is>
-          <t>pesoler</t>
+          <t>pesolre</t>
         </is>
       </c>
       <c r="B1913" t="inlineStr">
@@ -23423,7 +23423,7 @@
     <row r="1918">
       <c r="A1918" t="inlineStr">
         <is>
-          <t>policio</t>
+          <t>policer</t>
         </is>
       </c>
       <c r="B1918" t="inlineStr">
@@ -23435,7 +23435,7 @@
     <row r="1919">
       <c r="A1919" t="inlineStr">
         <is>
-          <t>Manelto</t>
+          <t>Manelio</t>
         </is>
       </c>
       <c r="B1919" t="inlineStr">
@@ -23447,7 +23447,7 @@
     <row r="1920">
       <c r="A1920" t="inlineStr">
         <is>
-          <t>bommpre</t>
+          <t>bommpio</t>
         </is>
       </c>
       <c r="B1920" t="inlineStr">
@@ -23483,7 +23483,7 @@
     <row r="1923">
       <c r="A1923" t="inlineStr">
         <is>
-          <t>poriner</t>
+          <t>porinre</t>
         </is>
       </c>
       <c r="B1923" t="inlineStr">
@@ -23495,7 +23495,7 @@
     <row r="1924">
       <c r="A1924" t="inlineStr">
         <is>
-          <t>porinto</t>
+          <t>porinio</t>
         </is>
       </c>
       <c r="B1924" t="inlineStr">
@@ -23555,7 +23555,7 @@
     <row r="1929">
       <c r="A1929" t="inlineStr">
         <is>
-          <t>potndio</t>
+          <t>potndre</t>
         </is>
       </c>
       <c r="B1929" t="inlineStr">
@@ -23651,7 +23651,7 @@
     <row r="1937">
       <c r="A1937" t="inlineStr">
         <is>
-          <t>praicer</t>
+          <t>praicre</t>
         </is>
       </c>
       <c r="B1937" t="inlineStr">
@@ -23723,7 +23723,7 @@
     <row r="1943">
       <c r="A1943" t="inlineStr">
         <is>
-          <t>prentio</t>
+          <t>prentre</t>
         </is>
       </c>
       <c r="B1943" t="inlineStr">
@@ -23843,7 +23843,7 @@
     <row r="1953">
       <c r="A1953" t="inlineStr">
         <is>
-          <t>prentto</t>
+          <t>prenter</t>
         </is>
       </c>
       <c r="B1953" t="inlineStr">
@@ -23855,7 +23855,7 @@
     <row r="1954">
       <c r="A1954" t="inlineStr">
         <is>
-          <t>sennsio</t>
+          <t>sennsre</t>
         </is>
       </c>
       <c r="B1954" t="inlineStr">
@@ -23939,7 +23939,7 @@
     <row r="1961">
       <c r="A1961" t="inlineStr">
         <is>
-          <t>esprsio</t>
+          <t>esprsto</t>
         </is>
       </c>
       <c r="B1961" t="inlineStr">
@@ -23975,7 +23975,7 @@
     <row r="1964">
       <c r="A1964" t="inlineStr">
         <is>
-          <t>prierto</t>
+          <t>prierer</t>
         </is>
       </c>
       <c r="B1964" t="inlineStr">
@@ -24011,7 +24011,7 @@
     <row r="1967">
       <c r="A1967" t="inlineStr">
         <is>
-          <t>prieger</t>
+          <t>priegre</t>
         </is>
       </c>
       <c r="B1967" t="inlineStr">
@@ -24059,7 +24059,7 @@
     <row r="1971">
       <c r="A1971" t="inlineStr">
         <is>
-          <t>proosio</t>
+          <t>proosto</t>
         </is>
       </c>
       <c r="B1971" t="inlineStr">
@@ -24071,7 +24071,7 @@
     <row r="1972">
       <c r="A1972" t="inlineStr">
         <is>
-          <t>proaner</t>
+          <t>proanio</t>
         </is>
       </c>
       <c r="B1972" t="inlineStr">
@@ -24083,7 +24083,7 @@
     <row r="1973">
       <c r="A1973" t="inlineStr">
         <is>
-          <t>darucio</t>
+          <t>darucer</t>
         </is>
       </c>
       <c r="B1973" t="inlineStr">
@@ -24131,7 +24131,7 @@
     <row r="1977">
       <c r="A1977" t="inlineStr">
         <is>
-          <t>prossre</t>
+          <t>prossio</t>
         </is>
       </c>
       <c r="B1977" t="inlineStr">
@@ -24191,7 +24191,7 @@
     <row r="1982">
       <c r="A1982" t="inlineStr">
         <is>
-          <t>pasatio</t>
+          <t>pasater</t>
         </is>
       </c>
       <c r="B1982" t="inlineStr">
@@ -24227,7 +24227,7 @@
     <row r="1985">
       <c r="A1985" t="inlineStr">
         <is>
-          <t>prooner</t>
+          <t>proonto</t>
         </is>
       </c>
       <c r="B1985" t="inlineStr">
@@ -24287,7 +24287,7 @@
     <row r="1990">
       <c r="A1990" t="inlineStr">
         <is>
-          <t>proivto</t>
+          <t>proivre</t>
         </is>
       </c>
       <c r="B1990" t="inlineStr">
@@ -24347,7 +24347,7 @@
     <row r="1995">
       <c r="A1995" t="inlineStr">
         <is>
-          <t>sur dto</t>
+          <t>sur dre</t>
         </is>
       </c>
       <c r="B1995" t="inlineStr">
@@ -24359,7 +24359,7 @@
     <row r="1996">
       <c r="A1996" t="inlineStr">
         <is>
-          <t>disonto</t>
+          <t>disonio</t>
         </is>
       </c>
       <c r="B1996" t="inlineStr">
@@ -24383,7 +24383,7 @@
     <row r="1998">
       <c r="A1998" t="inlineStr">
         <is>
-          <t>cirgnio</t>
+          <t>cirgner</t>
         </is>
       </c>
       <c r="B1998" t="inlineStr">
@@ -24407,7 +24407,7 @@
     <row r="2000">
       <c r="A2000" t="inlineStr">
         <is>
-          <t>poccher</t>
+          <t>pocchio</t>
         </is>
       </c>
       <c r="B2000" t="inlineStr">
@@ -24419,7 +24419,7 @@
     <row r="2001">
       <c r="A2001" t="inlineStr">
         <is>
-          <t>dibgnio</t>
+          <t>dibgnto</t>
         </is>
       </c>
       <c r="B2001" t="inlineStr">
@@ -24431,7 +24431,7 @@
     <row r="2002">
       <c r="A2002" t="inlineStr">
         <is>
-          <t>pulonto</t>
+          <t>pulonio</t>
         </is>
       </c>
       <c r="B2002" t="inlineStr">
@@ -24443,7 +24443,7 @@
     <row r="2003">
       <c r="A2003" t="inlineStr">
         <is>
-          <t>prierer</t>
+          <t>prierre</t>
         </is>
       </c>
       <c r="B2003" t="inlineStr">
@@ -24455,7 +24455,7 @@
     <row r="2004">
       <c r="A2004" t="inlineStr">
         <is>
-          <t>pullsio</t>
+          <t>pullsre</t>
         </is>
       </c>
       <c r="B2004" t="inlineStr">
@@ -24611,7 +24611,7 @@
     <row r="2017">
       <c r="A2017" t="inlineStr">
         <is>
-          <t>avireto</t>
+          <t>avireio</t>
         </is>
       </c>
       <c r="B2017" t="inlineStr">
@@ -24707,7 +24707,7 @@
     <row r="2025">
       <c r="A2025" t="inlineStr">
         <is>
-          <t>rábllto</t>
+          <t>rábllio</t>
         </is>
       </c>
       <c r="B2025" t="inlineStr">
@@ -24719,7 +24719,7 @@
     <row r="2026">
       <c r="A2026" t="inlineStr">
         <is>
-          <t>traonio</t>
+          <t>traonre</t>
         </is>
       </c>
       <c r="B2026" t="inlineStr">
@@ -24767,7 +24767,7 @@
     <row r="2030">
       <c r="A2030" t="inlineStr">
         <is>
-          <t>razivio</t>
+          <t>razivto</t>
         </is>
       </c>
       <c r="B2030" t="inlineStr">
@@ -24815,7 +24815,7 @@
     <row r="2034">
       <c r="A2034" t="inlineStr">
         <is>
-          <t>reullto</t>
+          <t>reullio</t>
         </is>
       </c>
       <c r="B2034" t="inlineStr">
@@ -24851,7 +24851,7 @@
     <row r="2037">
       <c r="A2037" t="inlineStr">
         <is>
-          <t>tratrto</t>
+          <t>tratrio</t>
         </is>
       </c>
       <c r="B2037" t="inlineStr">
@@ -24863,7 +24863,7 @@
     <row r="2038">
       <c r="A2038" t="inlineStr">
         <is>
-          <t>rammpio</t>
+          <t>rammper</t>
         </is>
       </c>
       <c r="B2038" t="inlineStr">
@@ -24959,7 +24959,7 @@
     <row r="2046">
       <c r="A2046" t="inlineStr">
         <is>
-          <t>infrtio</t>
+          <t>infrter</t>
         </is>
       </c>
       <c r="B2046" t="inlineStr">
@@ -24995,7 +24995,7 @@
     <row r="2049">
       <c r="A2049" t="inlineStr">
         <is>
-          <t>razzzer</t>
+          <t>razzzio</t>
         </is>
       </c>
       <c r="B2049" t="inlineStr">
@@ -25091,7 +25091,7 @@
     <row r="2057">
       <c r="A2057" t="inlineStr">
         <is>
-          <t>racntto</t>
+          <t>racnter</t>
         </is>
       </c>
       <c r="B2057" t="inlineStr">
@@ -25139,7 +25139,7 @@
     <row r="2061">
       <c r="A2061" t="inlineStr">
         <is>
-          <t>trainre</t>
+          <t>trainer</t>
         </is>
       </c>
       <c r="B2061" t="inlineStr">
@@ -25163,7 +25163,7 @@
     <row r="2063">
       <c r="A2063" t="inlineStr">
         <is>
-          <t>baroner</t>
+          <t>baronre</t>
         </is>
       </c>
       <c r="B2063" t="inlineStr">
@@ -25175,7 +25175,7 @@
     <row r="2064">
       <c r="A2064" t="inlineStr">
         <is>
-          <t>delzire</t>
+          <t>delziio</t>
         </is>
       </c>
       <c r="B2064" t="inlineStr">
@@ -25271,7 +25271,7 @@
     <row r="2072">
       <c r="A2072" t="inlineStr">
         <is>
-          <t>voltrto</t>
+          <t>voltrer</t>
         </is>
       </c>
       <c r="B2072" t="inlineStr">
@@ -25307,7 +25307,7 @@
     <row r="2075">
       <c r="A2075" t="inlineStr">
         <is>
-          <t>recoger</t>
+          <t>recogio</t>
         </is>
       </c>
       <c r="B2075" t="inlineStr">
@@ -25391,7 +25391,7 @@
     <row r="2082">
       <c r="A2082" t="inlineStr">
         <is>
-          <t>reiiver</t>
+          <t>reiivio</t>
         </is>
       </c>
       <c r="B2082" t="inlineStr">
@@ -25427,7 +25427,7 @@
     <row r="2085">
       <c r="A2085" t="inlineStr">
         <is>
-          <t>segicre</t>
+          <t>segicer</t>
         </is>
       </c>
       <c r="B2085" t="inlineStr">
@@ -25451,7 +25451,7 @@
     <row r="2087">
       <c r="A2087" t="inlineStr">
         <is>
-          <t>Reacito</t>
+          <t>Reacire</t>
         </is>
       </c>
       <c r="B2087" t="inlineStr">
@@ -25571,7 +25571,7 @@
     <row r="2097">
       <c r="A2097" t="inlineStr">
         <is>
-          <t>cubinto</t>
+          <t>cubiner</t>
         </is>
       </c>
       <c r="B2097" t="inlineStr">
@@ -25583,7 +25583,7 @@
     <row r="2098">
       <c r="A2098" t="inlineStr">
         <is>
-          <t>reconto</t>
+          <t>reconer</t>
         </is>
       </c>
       <c r="B2098" t="inlineStr">
@@ -25631,7 +25631,7 @@
     <row r="2102">
       <c r="A2102" t="inlineStr">
         <is>
-          <t>rettrer</t>
+          <t>rettrre</t>
         </is>
       </c>
       <c r="B2102" t="inlineStr">
@@ -25643,7 +25643,7 @@
     <row r="2103">
       <c r="A2103" t="inlineStr">
         <is>
-          <t>parrsio</t>
+          <t>parrser</t>
         </is>
       </c>
       <c r="B2103" t="inlineStr">
@@ -25667,7 +25667,7 @@
     <row r="2105">
       <c r="A2105" t="inlineStr">
         <is>
-          <t>reiinto</t>
+          <t>reiinre</t>
         </is>
       </c>
       <c r="B2105" t="inlineStr">
@@ -25799,7 +25799,7 @@
     <row r="2116">
       <c r="A2116" t="inlineStr">
         <is>
-          <t>refssio</t>
+          <t>refssre</t>
         </is>
       </c>
       <c r="B2116" t="inlineStr">
@@ -25835,7 +25835,7 @@
     <row r="2119">
       <c r="A2119" t="inlineStr">
         <is>
-          <t>refscto</t>
+          <t>refscre</t>
         </is>
       </c>
       <c r="B2119" t="inlineStr">
@@ -25847,7 +25847,7 @@
     <row r="2120">
       <c r="A2120" t="inlineStr">
         <is>
-          <t>referre</t>
+          <t>referto</t>
         </is>
       </c>
       <c r="B2120" t="inlineStr">
@@ -25859,7 +25859,7 @@
     <row r="2121">
       <c r="A2121" t="inlineStr">
         <is>
-          <t>Frddio</t>
+          <t>Frdder</t>
         </is>
       </c>
       <c r="B2121" t="inlineStr">
@@ -25919,7 +25919,7 @@
     <row r="2126">
       <c r="A2126" t="inlineStr">
         <is>
-          <t>estaler</t>
+          <t>estalre</t>
         </is>
       </c>
       <c r="B2126" t="inlineStr">
@@ -25943,7 +25943,7 @@
     <row r="2128">
       <c r="A2128" t="inlineStr">
         <is>
-          <t>regimio</t>
+          <t>regimre</t>
         </is>
       </c>
       <c r="B2128" t="inlineStr">
@@ -25955,7 +25955,7 @@
     <row r="2129">
       <c r="A2129" t="inlineStr">
         <is>
-          <t>noroler</t>
+          <t>norolio</t>
         </is>
       </c>
       <c r="B2129" t="inlineStr">
@@ -26075,7 +26075,7 @@
     <row r="2139">
       <c r="A2139" t="inlineStr">
         <is>
-          <t>aleuier</t>
+          <t>aleuito</t>
         </is>
       </c>
       <c r="B2139" t="inlineStr">
@@ -26087,7 +26087,7 @@
     <row r="2140">
       <c r="A2140" t="inlineStr">
         <is>
-          <t>rellato</t>
+          <t>rellaio</t>
         </is>
       </c>
       <c r="B2140" t="inlineStr">
@@ -26111,7 +26111,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>relonto</t>
+          <t>relonio</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">
@@ -26219,7 +26219,7 @@
     <row r="2151">
       <c r="A2151" t="inlineStr">
         <is>
-          <t>remedto</t>
+          <t>remeder</t>
         </is>
       </c>
       <c r="B2151" t="inlineStr">
@@ -26231,7 +26231,7 @@
     <row r="2152">
       <c r="A2152" t="inlineStr">
         <is>
-          <t>recrdto</t>
+          <t>recrdre</t>
         </is>
       </c>
       <c r="B2152" t="inlineStr">
@@ -26243,7 +26243,7 @@
     <row r="2153">
       <c r="A2153" t="inlineStr">
         <is>
-          <t>agrziio</t>
+          <t>agrzito</t>
         </is>
       </c>
       <c r="B2153" t="inlineStr">
@@ -26303,7 +26303,7 @@
     <row r="2158">
       <c r="A2158" t="inlineStr">
         <is>
-          <t>ganiter</t>
+          <t>ganitre</t>
         </is>
       </c>
       <c r="B2158" t="inlineStr">
@@ -26315,7 +26315,7 @@
     <row r="2159">
       <c r="A2159" t="inlineStr">
         <is>
-          <t>remater</t>
+          <t>rematto</t>
         </is>
       </c>
       <c r="B2159" t="inlineStr">
@@ -26339,7 +26339,7 @@
     <row r="2161">
       <c r="A2161" t="inlineStr">
         <is>
-          <t>renrier</t>
+          <t>renriio</t>
         </is>
       </c>
       <c r="B2161" t="inlineStr">
@@ -26411,7 +26411,7 @@
     <row r="2167">
       <c r="A2167" t="inlineStr">
         <is>
-          <t>Renoiio</t>
+          <t>Renoier</t>
         </is>
       </c>
       <c r="B2167" t="inlineStr">
@@ -26435,7 +26435,7 @@
     <row r="2169">
       <c r="A2169" t="inlineStr">
         <is>
-          <t>recrsto</t>
+          <t>recrsre</t>
         </is>
       </c>
       <c r="B2169" t="inlineStr">
@@ -26519,7 +26519,7 @@
     <row r="2176">
       <c r="A2176" t="inlineStr">
         <is>
-          <t>envtrer</t>
+          <t>envtrio</t>
         </is>
       </c>
       <c r="B2176" t="inlineStr">
@@ -26603,7 +26603,7 @@
     <row r="2183">
       <c r="A2183" t="inlineStr">
         <is>
-          <t>reponre</t>
+          <t>reponio</t>
         </is>
       </c>
       <c r="B2183" t="inlineStr">
@@ -26651,7 +26651,7 @@
     <row r="2187">
       <c r="A2187" t="inlineStr">
         <is>
-          <t>dobegio</t>
+          <t>dobegre</t>
         </is>
       </c>
       <c r="B2187" t="inlineStr">
@@ -26735,7 +26735,7 @@
     <row r="2194">
       <c r="A2194" t="inlineStr">
         <is>
-          <t>reperre</t>
+          <t>reperio</t>
         </is>
       </c>
       <c r="B2194" t="inlineStr">
@@ -26759,7 +26759,7 @@
     <row r="2196">
       <c r="A2196" t="inlineStr">
         <is>
-          <t>replato</t>
+          <t>replaer</t>
         </is>
       </c>
       <c r="B2196" t="inlineStr">
@@ -26795,7 +26795,7 @@
     <row r="2199">
       <c r="A2199" t="inlineStr">
         <is>
-          <t>repnter</t>
+          <t>repntre</t>
         </is>
       </c>
       <c r="B2199" t="inlineStr">
@@ -26819,7 +26819,7 @@
     <row r="2201">
       <c r="A2201" t="inlineStr">
         <is>
-          <t>resrvre</t>
+          <t>resrver</t>
         </is>
       </c>
       <c r="B2201" t="inlineStr">
@@ -26843,7 +26843,7 @@
     <row r="2203">
       <c r="A2203" t="inlineStr">
         <is>
-          <t>resntre</t>
+          <t>resnter</t>
         </is>
       </c>
       <c r="B2203" t="inlineStr">
@@ -26855,7 +26855,7 @@
     <row r="2204">
       <c r="A2204" t="inlineStr">
         <is>
-          <t>renssto</t>
+          <t>renssio</t>
         </is>
       </c>
       <c r="B2204" t="inlineStr">
@@ -26891,7 +26891,7 @@
     <row r="2207">
       <c r="A2207" t="inlineStr">
         <is>
-          <t>razivto</t>
+          <t>raziver</t>
         </is>
       </c>
       <c r="B2207" t="inlineStr">
@@ -27047,7 +27047,7 @@
     <row r="2220">
       <c r="A2220" t="inlineStr">
         <is>
-          <t>curluio</t>
+          <t>curluto</t>
         </is>
       </c>
       <c r="B2220" t="inlineStr">
@@ -27155,7 +27155,7 @@
     <row r="2229">
       <c r="A2229" t="inlineStr">
         <is>
-          <t>devrnre</t>
+          <t>devrnio</t>
         </is>
       </c>
       <c r="B2229" t="inlineStr">
@@ -27203,7 +27203,7 @@
     <row r="2233">
       <c r="A2233" t="inlineStr">
         <is>
-          <t>retader</t>
+          <t>retadre</t>
         </is>
       </c>
       <c r="B2233" t="inlineStr">
@@ -27227,7 +27227,7 @@
     <row r="2235">
       <c r="A2235" t="inlineStr">
         <is>
-          <t>reuunre</t>
+          <t>reuuner</t>
         </is>
       </c>
       <c r="B2235" t="inlineStr">
@@ -27299,7 +27299,7 @@
     <row r="2241">
       <c r="A2241" t="inlineStr">
         <is>
-          <t>jueolto</t>
+          <t>jueoler</t>
         </is>
       </c>
       <c r="B2241" t="inlineStr">
@@ -27347,7 +27347,7 @@
     <row r="2245">
       <c r="A2245" t="inlineStr">
         <is>
-          <t>reverer</t>
+          <t>reverto</t>
         </is>
       </c>
       <c r="B2245" t="inlineStr">
@@ -27359,7 +27359,7 @@
     <row r="2246">
       <c r="A2246" t="inlineStr">
         <is>
-          <t>revntto</t>
+          <t>revntre</t>
         </is>
       </c>
       <c r="B2246" t="inlineStr">
@@ -27371,7 +27371,7 @@
     <row r="2247">
       <c r="A2247" t="inlineStr">
         <is>
-          <t>revveto</t>
+          <t>revveio</t>
         </is>
       </c>
       <c r="B2247" t="inlineStr">
@@ -27407,7 +27407,7 @@
     <row r="2250">
       <c r="A2250" t="inlineStr">
         <is>
-          <t>adircer</t>
+          <t>adircre</t>
         </is>
       </c>
       <c r="B2250" t="inlineStr">
@@ -27419,7 +27419,7 @@
     <row r="2251">
       <c r="A2251" t="inlineStr">
         <is>
-          <t>revlter</t>
+          <t>revltio</t>
         </is>
       </c>
       <c r="B2251" t="inlineStr">
@@ -27431,7 +27431,7 @@
     <row r="2252">
       <c r="A2252" t="inlineStr">
         <is>
-          <t>revllre</t>
+          <t>revller</t>
         </is>
       </c>
       <c r="B2252" t="inlineStr">
@@ -27443,7 +27443,7 @@
     <row r="2253">
       <c r="A2253" t="inlineStr">
         <is>
-          <t>burgner</t>
+          <t>burgnio</t>
         </is>
       </c>
       <c r="B2253" t="inlineStr">
@@ -27467,7 +27467,7 @@
     <row r="2255">
       <c r="A2255" t="inlineStr">
         <is>
-          <t>ridolto</t>
+          <t>ridoler</t>
         </is>
       </c>
       <c r="B2255" t="inlineStr">
@@ -27491,7 +27491,7 @@
     <row r="2257">
       <c r="A2257" t="inlineStr">
         <is>
-          <t>enjquio</t>
+          <t>enjquer</t>
         </is>
       </c>
       <c r="B2257" t="inlineStr">
@@ -27503,7 +27503,7 @@
     <row r="2258">
       <c r="A2258" t="inlineStr">
         <is>
-          <t>másurre</t>
+          <t>másurer</t>
         </is>
       </c>
       <c r="B2258" t="inlineStr">
@@ -27671,7 +27671,7 @@
     <row r="2272">
       <c r="A2272" t="inlineStr">
         <is>
-          <t>tuber</t>
+          <t>tubre</t>
         </is>
       </c>
       <c r="B2272" t="inlineStr">
@@ -27683,7 +27683,7 @@
     <row r="2273">
       <c r="A2273" t="inlineStr">
         <is>
-          <t>brinzio</t>
+          <t>brinzre</t>
         </is>
       </c>
       <c r="B2273" t="inlineStr">
@@ -27707,7 +27707,7 @@
     <row r="2275">
       <c r="A2275" t="inlineStr">
         <is>
-          <t>óxiinio</t>
+          <t>óxiinre</t>
         </is>
       </c>
       <c r="B2275" t="inlineStr">
@@ -27755,7 +27755,7 @@
     <row r="2279">
       <c r="A2279" t="inlineStr">
         <is>
-          <t>queurer</t>
+          <t>queurio</t>
         </is>
       </c>
       <c r="B2279" t="inlineStr">
@@ -27767,7 +27767,7 @@
     <row r="2280">
       <c r="A2280" t="inlineStr">
         <is>
-          <t>camader</t>
+          <t>camadio</t>
         </is>
       </c>
       <c r="B2280" t="inlineStr">
@@ -27815,7 +27815,7 @@
     <row r="2284">
       <c r="A2284" t="inlineStr">
         <is>
-          <t>resinio</t>
+          <t>resinre</t>
         </is>
       </c>
       <c r="B2284" t="inlineStr">
@@ -27935,7 +27935,7 @@
     <row r="2294">
       <c r="A2294" t="inlineStr">
         <is>
-          <t>estonio</t>
+          <t>estonre</t>
         </is>
       </c>
       <c r="B2294" t="inlineStr">
@@ -27947,7 +27947,7 @@
     <row r="2295">
       <c r="A2295" t="inlineStr">
         <is>
-          <t>sler</t>
+          <t>slre</t>
         </is>
       </c>
       <c r="B2295" t="inlineStr">
@@ -27959,7 +27959,7 @@
     <row r="2296">
       <c r="A2296" t="inlineStr">
         <is>
-          <t>salcer</t>
+          <t>salcto</t>
         </is>
       </c>
       <c r="B2296" t="inlineStr">
@@ -27983,7 +27983,7 @@
     <row r="2298">
       <c r="A2298" t="inlineStr">
         <is>
-          <t>sanonre</t>
+          <t>sanoner</t>
         </is>
       </c>
       <c r="B2298" t="inlineStr">
@@ -27995,7 +27995,7 @@
     <row r="2299">
       <c r="A2299" t="inlineStr">
         <is>
-          <t>jabaler</t>
+          <t>jabalto</t>
         </is>
       </c>
       <c r="B2299" t="inlineStr">
@@ -28055,7 +28055,7 @@
     <row r="2304">
       <c r="A2304" t="inlineStr">
         <is>
-          <t>ancomer</t>
+          <t>ancomto</t>
         </is>
       </c>
       <c r="B2304" t="inlineStr">
@@ -28115,7 +28115,7 @@
     <row r="2309">
       <c r="A2309" t="inlineStr">
         <is>
-          <t>aholvio</t>
+          <t>aholvre</t>
         </is>
       </c>
       <c r="B2309" t="inlineStr">
@@ -28127,7 +28127,7 @@
     <row r="2310">
       <c r="A2310" t="inlineStr">
         <is>
-          <t>jabonre</t>
+          <t>jabonio</t>
         </is>
       </c>
       <c r="B2310" t="inlineStr">
@@ -28187,7 +28187,7 @@
     <row r="2315">
       <c r="A2315" t="inlineStr">
         <is>
-          <t>selcto</t>
+          <t>selcre</t>
         </is>
       </c>
       <c r="B2315" t="inlineStr">
@@ -28223,7 +28223,7 @@
     <row r="2318">
       <c r="A2318" t="inlineStr">
         <is>
-          <t>siegto</t>
+          <t>siegio</t>
         </is>
       </c>
       <c r="B2318" t="inlineStr">
@@ -28235,7 +28235,7 @@
     <row r="2319">
       <c r="A2319" t="inlineStr">
         <is>
-          <t>diviser</t>
+          <t>divisio</t>
         </is>
       </c>
       <c r="B2319" t="inlineStr">
@@ -28283,7 +28283,7 @@
     <row r="2323">
       <c r="A2323" t="inlineStr">
         <is>
-          <t>conurre</t>
+          <t>conurto</t>
         </is>
       </c>
       <c r="B2323" t="inlineStr">
@@ -28403,7 +28403,7 @@
     <row r="2333">
       <c r="A2333" t="inlineStr">
         <is>
-          <t>camerre</t>
+          <t>camerto</t>
         </is>
       </c>
       <c r="B2333" t="inlineStr">
@@ -28451,7 +28451,7 @@
     <row r="2337">
       <c r="A2337" t="inlineStr">
         <is>
-          <t>connzio</t>
+          <t>connzto</t>
         </is>
       </c>
       <c r="B2337" t="inlineStr">
@@ -28511,7 +28511,7 @@
     <row r="2342">
       <c r="A2342" t="inlineStr">
         <is>
-          <t>shamiio</t>
+          <t>shamito</t>
         </is>
       </c>
       <c r="B2342" t="inlineStr">
@@ -28583,7 +28583,7 @@
     <row r="2348">
       <c r="A2348" t="inlineStr">
         <is>
-          <t>signtre</t>
+          <t>signtio</t>
         </is>
       </c>
       <c r="B2348" t="inlineStr">
@@ -28703,7 +28703,7 @@
     <row r="2358">
       <c r="A2358" t="inlineStr">
         <is>
-          <t>cuirre</t>
+          <t>cuirto</t>
         </is>
       </c>
       <c r="B2358" t="inlineStr">
@@ -28751,7 +28751,7 @@
     <row r="2362">
       <c r="A2362" t="inlineStr">
         <is>
-          <t>hunller</t>
+          <t>hunllto</t>
         </is>
       </c>
       <c r="B2362" t="inlineStr">
@@ -28787,7 +28787,7 @@
     <row r="2365">
       <c r="A2365" t="inlineStr">
         <is>
-          <t>snzer</t>
+          <t>snzio</t>
         </is>
       </c>
       <c r="B2365" t="inlineStr">
@@ -28811,7 +28811,7 @@
     <row r="2367">
       <c r="A2367" t="inlineStr">
         <is>
-          <t>aniller</t>
+          <t>anillto</t>
         </is>
       </c>
       <c r="B2367" t="inlineStr">
@@ -28847,7 +28847,7 @@
     <row r="2370">
       <c r="A2370" t="inlineStr">
         <is>
-          <t>preonre</t>
+          <t>preonio</t>
         </is>
       </c>
       <c r="B2370" t="inlineStr">
@@ -28871,7 +28871,7 @@
     <row r="2372">
       <c r="A2372" t="inlineStr">
         <is>
-          <t>sobnter</t>
+          <t>sobntio</t>
         </is>
       </c>
       <c r="B2372" t="inlineStr">
@@ -29027,7 +29027,7 @@
     <row r="2385">
       <c r="A2385" t="inlineStr">
         <is>
-          <t>susirto</t>
+          <t>susirer</t>
         </is>
       </c>
       <c r="B2385" t="inlineStr">
@@ -29087,7 +29087,7 @@
     <row r="2390">
       <c r="A2390" t="inlineStr">
         <is>
-          <t>recnire</t>
+          <t>recnito</t>
         </is>
       </c>
       <c r="B2390" t="inlineStr">
@@ -29099,7 +29099,7 @@
     <row r="2391">
       <c r="A2391" t="inlineStr">
         <is>
-          <t>vocntio</t>
+          <t>vocntto</t>
         </is>
       </c>
       <c r="B2391" t="inlineStr">
@@ -29123,7 +29123,7 @@
     <row r="2393">
       <c r="A2393" t="inlineStr">
         <is>
-          <t>regolre</t>
+          <t>regoler</t>
         </is>
       </c>
       <c r="B2393" t="inlineStr">
@@ -29147,7 +29147,7 @@
     <row r="2395">
       <c r="A2395" t="inlineStr">
         <is>
-          <t>alminer</t>
+          <t>alminto</t>
         </is>
       </c>
       <c r="B2395" t="inlineStr">
@@ -29159,7 +29159,7 @@
     <row r="2396">
       <c r="A2396" t="inlineStr">
         <is>
-          <t>tappper</t>
+          <t>tapppto</t>
         </is>
       </c>
       <c r="B2396" t="inlineStr">
@@ -29183,7 +29183,7 @@
     <row r="2398">
       <c r="A2398" t="inlineStr">
         <is>
-          <t>estntto</t>
+          <t>estntio</t>
         </is>
       </c>
       <c r="B2398" t="inlineStr">
@@ -29315,7 +29315,7 @@
     <row r="2409">
       <c r="A2409" t="inlineStr">
         <is>
-          <t>azúerio</t>
+          <t>azúerre</t>
         </is>
       </c>
       <c r="B2409" t="inlineStr">
@@ -29411,7 +29411,7 @@
     <row r="2417">
       <c r="A2417" t="inlineStr">
         <is>
-          <t>másilio</t>
+          <t>másilre</t>
         </is>
       </c>
       <c r="B2417" t="inlineStr">
@@ -29471,7 +29471,7 @@
     <row r="2422">
       <c r="A2422" t="inlineStr">
         <is>
-          <t>BORARre</t>
+          <t>BORARio</t>
         </is>
       </c>
       <c r="B2422" t="inlineStr">
@@ -29483,7 +29483,7 @@
     <row r="2423">
       <c r="A2423" t="inlineStr">
         <is>
-          <t>supntio</t>
+          <t>supnter</t>
         </is>
       </c>
       <c r="B2423" t="inlineStr">
@@ -29519,7 +29519,7 @@
     <row r="2426">
       <c r="A2426" t="inlineStr">
         <is>
-          <t>sobatto</t>
+          <t>sobatre</t>
         </is>
       </c>
       <c r="B2426" t="inlineStr">
@@ -29543,7 +29543,7 @@
     <row r="2428">
       <c r="A2428" t="inlineStr">
         <is>
-          <t>valrtio</t>
+          <t>valrtre</t>
         </is>
       </c>
       <c r="B2428" t="inlineStr">
@@ -29591,7 +29591,7 @@
     <row r="2432">
       <c r="A2432" t="inlineStr">
         <is>
-          <t>apoomto</t>
+          <t>apoomer</t>
         </is>
       </c>
       <c r="B2432" t="inlineStr">
@@ -29687,7 +29687,7 @@
     <row r="2440">
       <c r="A2440" t="inlineStr">
         <is>
-          <t>susrrto</t>
+          <t>susrrre</t>
         </is>
       </c>
       <c r="B2440" t="inlineStr">
@@ -29723,7 +29723,7 @@
     <row r="2443">
       <c r="A2443" t="inlineStr">
         <is>
-          <t>delulio</t>
+          <t>delulre</t>
         </is>
       </c>
       <c r="B2443" t="inlineStr">
@@ -29735,7 +29735,7 @@
     <row r="2444">
       <c r="A2444" t="inlineStr">
         <is>
-          <t>manhier</t>
+          <t>manhito</t>
         </is>
       </c>
       <c r="B2444" t="inlineStr">
@@ -29747,7 +29747,7 @@
     <row r="2445">
       <c r="A2445" t="inlineStr">
         <is>
-          <t>cirssio</t>
+          <t>cirssto</t>
         </is>
       </c>
       <c r="B2445" t="inlineStr">
@@ -29795,7 +29795,7 @@
     <row r="2449">
       <c r="A2449" t="inlineStr">
         <is>
-          <t>petrnto</t>
+          <t>petrnre</t>
         </is>
       </c>
       <c r="B2449" t="inlineStr">
@@ -29807,7 +29807,7 @@
     <row r="2450">
       <c r="A2450" t="inlineStr">
         <is>
-          <t>Tánerer</t>
+          <t>Tánerio</t>
         </is>
       </c>
       <c r="B2450" t="inlineStr">
@@ -29843,7 +29843,7 @@
     <row r="2453">
       <c r="A2453" t="inlineStr">
         <is>
-          <t>afiitre</t>
+          <t>afiitto</t>
         </is>
       </c>
       <c r="B2453" t="inlineStr">
@@ -29855,7 +29855,7 @@
     <row r="2454">
       <c r="A2454" t="inlineStr">
         <is>
-          <t>fasonre</t>
+          <t>fasonto</t>
         </is>
       </c>
       <c r="B2454" t="inlineStr">
@@ -29867,7 +29867,7 @@
     <row r="2455">
       <c r="A2455" t="inlineStr">
         <is>
-          <t>demrder</t>
+          <t>demrdio</t>
         </is>
       </c>
       <c r="B2455" t="inlineStr">
@@ -29891,7 +29891,7 @@
     <row r="2457">
       <c r="A2457" t="inlineStr">
         <is>
-          <t>aprgiio</t>
+          <t>aprgito</t>
         </is>
       </c>
       <c r="B2457" t="inlineStr">
@@ -29939,7 +29939,7 @@
     <row r="2461">
       <c r="A2461" t="inlineStr">
         <is>
-          <t>impster</t>
+          <t>impstre</t>
         </is>
       </c>
       <c r="B2461" t="inlineStr">
@@ -29963,7 +29963,7 @@
     <row r="2463">
       <c r="A2463" t="inlineStr">
         <is>
-          <t>el stio</t>
+          <t>el ster</t>
         </is>
       </c>
       <c r="B2463" t="inlineStr">
@@ -30071,7 +30071,7 @@
     <row r="2472">
       <c r="A2472" t="inlineStr">
         <is>
-          <t>teroire</t>
+          <t>teroiio</t>
         </is>
       </c>
       <c r="B2472" t="inlineStr">
@@ -30263,7 +30263,7 @@
     <row r="2488">
       <c r="A2488" t="inlineStr">
         <is>
-          <t>toner</t>
+          <t>tonre</t>
         </is>
       </c>
       <c r="B2488" t="inlineStr">
@@ -30275,7 +30275,7 @@
     <row r="2489">
       <c r="A2489" t="inlineStr">
         <is>
-          <t>tonatio</t>
+          <t>tonatre</t>
         </is>
       </c>
       <c r="B2489" t="inlineStr">
@@ -30299,7 +30299,7 @@
     <row r="2491">
       <c r="A2491" t="inlineStr">
         <is>
-          <t>antcier</t>
+          <t>antcire</t>
         </is>
       </c>
       <c r="B2491" t="inlineStr">
@@ -30323,7 +30323,7 @@
     <row r="2493">
       <c r="A2493" t="inlineStr">
         <is>
-          <t>retrser</t>
+          <t>retrsto</t>
         </is>
       </c>
       <c r="B2493" t="inlineStr">
@@ -30431,7 +30431,7 @@
     <row r="2502">
       <c r="A2502" t="inlineStr">
         <is>
-          <t>tráicer</t>
+          <t>tráicto</t>
         </is>
       </c>
       <c r="B2502" t="inlineStr">
@@ -30515,7 +30515,7 @@
     <row r="2509">
       <c r="A2509" t="inlineStr">
         <is>
-          <t>trantre</t>
+          <t>trantio</t>
         </is>
       </c>
       <c r="B2509" t="inlineStr">
@@ -30683,7 +30683,7 @@
     <row r="2523">
       <c r="A2523" t="inlineStr">
         <is>
-          <t>traccto</t>
+          <t>traccre</t>
         </is>
       </c>
       <c r="B2523" t="inlineStr">
@@ -30791,7 +30791,7 @@
     <row r="2532">
       <c r="A2532" t="inlineStr">
         <is>
-          <t>engonto</t>
+          <t>engoner</t>
         </is>
       </c>
       <c r="B2532" t="inlineStr">
@@ -30803,7 +30803,7 @@
     <row r="2533">
       <c r="A2533" t="inlineStr">
         <is>
-          <t>tejlier</t>
+          <t>tejliio</t>
         </is>
       </c>
       <c r="B2533" t="inlineStr">
@@ -30827,7 +30827,7 @@
     <row r="2535">
       <c r="A2535" t="inlineStr">
         <is>
-          <t>tríerre</t>
+          <t>tríerer</t>
         </is>
       </c>
       <c r="B2535" t="inlineStr">
@@ -30863,7 +30863,7 @@
     <row r="2538">
       <c r="A2538" t="inlineStr">
         <is>
-          <t>vioinio</t>
+          <t>vioinre</t>
         </is>
       </c>
       <c r="B2538" t="inlineStr">
@@ -30887,7 +30887,7 @@
     <row r="2540">
       <c r="A2540" t="inlineStr">
         <is>
-          <t>perutio</t>
+          <t>peruter</t>
         </is>
       </c>
       <c r="B2540" t="inlineStr">
@@ -30899,7 +30899,7 @@
     <row r="2541">
       <c r="A2541" t="inlineStr">
         <is>
-          <t>aceedto</t>
+          <t>aceeder</t>
         </is>
       </c>
       <c r="B2541" t="inlineStr">
@@ -30971,7 +30971,7 @@
     <row r="2547">
       <c r="A2547" t="inlineStr">
         <is>
-          <t>matoner</t>
+          <t>matonto</t>
         </is>
       </c>
       <c r="B2547" t="inlineStr">
@@ -31067,7 +31067,7 @@
     <row r="2555">
       <c r="A2555" t="inlineStr">
         <is>
-          <t>usunter</t>
+          <t>usuntto</t>
         </is>
       </c>
       <c r="B2555" t="inlineStr">
@@ -31079,7 +31079,7 @@
     <row r="2556">
       <c r="A2556" t="inlineStr">
         <is>
-          <t>usuntio</t>
+          <t>usuntto</t>
         </is>
       </c>
       <c r="B2556" t="inlineStr">
@@ -31091,7 +31091,7 @@
     <row r="2557">
       <c r="A2557" t="inlineStr">
         <is>
-          <t>máqiner</t>
+          <t>máqinio</t>
         </is>
       </c>
       <c r="B2557" t="inlineStr">
@@ -31151,7 +31151,7 @@
     <row r="2562">
       <c r="A2562" t="inlineStr">
         <is>
-          <t>deaatio</t>
+          <t>deaater</t>
         </is>
       </c>
       <c r="B2562" t="inlineStr">
@@ -31187,7 +31187,7 @@
     <row r="2565">
       <c r="A2565" t="inlineStr">
         <is>
-          <t>aguquio</t>
+          <t>aguquer</t>
         </is>
       </c>
       <c r="B2565" t="inlineStr">
@@ -31199,7 +31199,7 @@
     <row r="2566">
       <c r="A2566" t="inlineStr">
         <is>
-          <t>prersre</t>
+          <t>prerser</t>
         </is>
       </c>
       <c r="B2566" t="inlineStr">
@@ -31235,7 +31235,7 @@
     <row r="2569">
       <c r="A2569" t="inlineStr">
         <is>
-          <t>veholto</t>
+          <t>veholer</t>
         </is>
       </c>
       <c r="B2569" t="inlineStr">
@@ -31259,7 +31259,7 @@
     <row r="2571">
       <c r="A2571" t="inlineStr">
         <is>
-          <t>venner</t>
+          <t>vennre</t>
         </is>
       </c>
       <c r="B2571" t="inlineStr">
@@ -31271,7 +31271,7 @@
     <row r="2572">
       <c r="A2572" t="inlineStr">
         <is>
-          <t>venttre</t>
+          <t>ventter</t>
         </is>
       </c>
       <c r="B2572" t="inlineStr">
@@ -31307,7 +31307,7 @@
     <row r="2575">
       <c r="A2575" t="inlineStr">
         <is>
-          <t>vto</t>
+          <t>ver</t>
         </is>
       </c>
       <c r="B2575" t="inlineStr">
@@ -31343,7 +31343,7 @@
     <row r="2578">
       <c r="A2578" t="inlineStr">
         <is>
-          <t>baricio</t>
+          <t>baricer</t>
         </is>
       </c>
       <c r="B2578" t="inlineStr">
@@ -31367,7 +31367,7 @@
     <row r="2580">
       <c r="A2580" t="inlineStr">
         <is>
-          <t>vetlire</t>
+          <t>vetlier</t>
         </is>
       </c>
       <c r="B2580" t="inlineStr">
@@ -31391,7 +31391,7 @@
     <row r="2582">
       <c r="A2582" t="inlineStr">
         <is>
-          <t>vejntre</t>
+          <t>vejntto</t>
         </is>
       </c>
       <c r="B2582" t="inlineStr">
@@ -31487,7 +31487,7 @@
     <row r="2590">
       <c r="A2590" t="inlineStr">
         <is>
-          <t>fueocer</t>
+          <t>fueocto</t>
         </is>
       </c>
       <c r="B2590" t="inlineStr">
@@ -31499,7 +31499,7 @@
     <row r="2591">
       <c r="A2591" t="inlineStr">
         <is>
-          <t>mueolre</t>
+          <t>mueoler</t>
         </is>
       </c>
       <c r="B2591" t="inlineStr">
@@ -31511,7 +31511,7 @@
     <row r="2592">
       <c r="A2592" t="inlineStr">
         <is>
-          <t>visiter</t>
+          <t>visitto</t>
         </is>
       </c>
       <c r="B2592" t="inlineStr">
@@ -31535,7 +31535,7 @@
     <row r="2594">
       <c r="A2594" t="inlineStr">
         <is>
-          <t>estscer</t>
+          <t>estscto</t>
         </is>
       </c>
       <c r="B2594" t="inlineStr">
@@ -31547,7 +31547,7 @@
     <row r="2595">
       <c r="A2595" t="inlineStr">
         <is>
-          <t>Vlamier</t>
+          <t>Vlamire</t>
         </is>
       </c>
       <c r="B2595" t="inlineStr">
@@ -31571,7 +31571,7 @@
     <row r="2597">
       <c r="A2597" t="inlineStr">
         <is>
-          <t>navlto</t>
+          <t>navlio</t>
         </is>
       </c>
       <c r="B2597" t="inlineStr">
@@ -31799,7 +31799,7 @@
     <row r="2616">
       <c r="A2616" t="inlineStr">
         <is>
-          <t>herstre</t>
+          <t>herster</t>
         </is>
       </c>
       <c r="B2616" t="inlineStr">
